--- a/jira_export_2026-06-30.xlsx
+++ b/jira_export_2026-06-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>69,212 €</t>
+          <t>69,339 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>24,237 €</t>
+          <t>24,365 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>779 h</t>
+          <t>778 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -898,7 +898,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -8963,10 +8963,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="13" t="n">
-        <v>0</v>
+        <v>127.8</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>0</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="116">
@@ -14477,10 +14477,10 @@
         <v>66535.84</v>
       </c>
       <c r="O202" s="19" t="n">
-        <v>69211.538</v>
+        <v>69339.33799999999</v>
       </c>
       <c r="P202" s="19" t="n">
-        <v>139.89</v>
+        <v>140.15</v>
       </c>
     </row>
   </sheetData>
@@ -16010,16 +16010,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>393793</v>
+        <v>393665</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>199704</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>194089</v>
+        <v>193961</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>162729</v>
+        <v>162601</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16035,16 +16035,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>194697</v>
+        <v>194570</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>90065</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>104632</v>
+        <v>104505</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>97124</v>
+        <v>96996</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>3060</v>
@@ -17806,7 +17806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -17827,7 +17827,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25 clôture(s) : 19 projet(s), 6 rework</t>
+          <t>26 clôture(s) : 20 projet(s), 6 rework</t>
         </is>
       </c>
     </row>
@@ -18407,17 +18407,17 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -18435,49 +18435,49 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-17131</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>[PAU] Migration GEODP</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>PAU</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F24" s="28" t="n">
-        <v>20</v>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33471</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE D AUCH</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-21265</t>
+          <t>PDMDEP-17131</t>
         </is>
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
+          <t>[PAU] Migration GEODP</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>SANARY SUR MER</t>
+          <t>PAU</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -18491,23 +18491,23 @@
         </is>
       </c>
       <c r="F25" s="28" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-23419</t>
+          <t>PDMDEP-21265</t>
         </is>
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN - GEODP2 migratio</t>
+          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN</t>
+          <t>SANARY SUR MER</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -18521,28 +18521,28 @@
         </is>
       </c>
       <c r="F26" s="28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-14779</t>
+          <t>PDMDEP-23419</t>
         </is>
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>[ANTIBES] Réinstallation Littéralis base Test et Prod</t>
+          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN - GEODP2 migratio</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E27" s="28" t="inlineStr">
@@ -18551,23 +18551,23 @@
         </is>
       </c>
       <c r="F27" s="28" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-23410</t>
+          <t>PDMDEP-14779</t>
         </is>
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+          <t>[ANTIBES] Réinstallation Littéralis base Test et Prod</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
@@ -18581,65 +18581,95 @@
         </is>
       </c>
       <c r="F28" s="28" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-23410</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-24216</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
-      <c r="C29" s="28" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="F30" s="28" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="29" t="n"/>
-      <c r="E32" s="29" t="n"/>
-      <c r="F32" s="29" t="n">
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="29" t="n">
         <v>6</v>
       </c>
     </row>

--- a/jira_export_2026-06-30.xlsx
+++ b/jira_export_2026-06-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>69,339 €</t>
+          <t>71,354 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>24,365 €</t>
+          <t>26,179 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>44,975 €</t>
+          <t>45,175 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P202"/>
+  <dimension ref="A1:P203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2273,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0</v>
+        <v>1312.5</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="22">
@@ -3048,11 +3048,11 @@
       <c r="N32" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="O32" s="17" t="n">
-        <v>1350</v>
+      <c r="O32" s="16" t="n">
+        <v>1500</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="33">
@@ -4744,11 +4744,11 @@
       <c r="N56" s="16" t="n">
         <v>184.5</v>
       </c>
-      <c r="O56" s="17" t="n">
-        <v>0</v>
+      <c r="O56" s="16" t="n">
+        <v>332.1</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0</v>
+        <v>1328.4</v>
       </c>
     </row>
     <row r="57">
@@ -4970,27 +4970,27 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32860</t>
+          <t>PDMDEP-32902</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LE LUC EN PROVENCE</t>
+          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION SIMPLE GEODP PLACIER</t>
+          <t xml:space="preserve">COMMANDE PAX </t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5005,64 +5005,64 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32869</t>
+          <t>PDMDEP-32910</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00164607</t>
+          <t>00159637</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>490</v>
-      </c>
-      <c r="O60" s="17" t="n">
-        <v>343</v>
+        <v>0</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>68.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -5077,49 +5077,49 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32869</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00164607</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>300</v>
+        <v>490</v>
       </c>
       <c r="O61" s="17" t="n">
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="P61" s="13" t="n">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5154,59 +5154,59 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="O62" s="16" t="n">
-        <v>2560</v>
+        <v>300</v>
+      </c>
+      <c r="O62" s="17" t="n">
+        <v>150</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5221,69 +5221,69 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>1984.5</v>
+        <v>800</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>1984.5</v>
+        <v>2560</v>
       </c>
       <c r="P63" s="13" t="n">
-        <v>360.82</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5293,69 +5293,69 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>1371</v>
-      </c>
-      <c r="O64" s="17" t="n">
-        <v>0</v>
+        <v>1984.5</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>1984.5</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>0</v>
+        <v>360.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
@@ -5377,101 +5377,109 @@
         <v>2</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>3864</v>
+        <v>1371</v>
       </c>
       <c r="O65" s="17" t="n">
-        <v>2484</v>
+        <v>0</v>
       </c>
       <c r="P65" s="13" t="n">
-        <v>709.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L66" s="15" t="inlineStr"/>
-      <c r="M66" s="15" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="L66" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32607</t>
+        </is>
+      </c>
+      <c r="M66" s="15" t="inlineStr">
+        <is>
+          <t>00163155</t>
+        </is>
+      </c>
       <c r="N66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="16" t="n">
-        <v>0</v>
+        <v>3864</v>
+      </c>
+      <c r="O66" s="17" t="n">
+        <v>2484</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0</v>
+        <v>709.71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5481,12 +5489,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5496,7 +5504,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -5513,22 +5521,14 @@
         <v>2</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L67" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M67" s="12" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L67" s="12" t="inlineStr"/>
+      <c r="M67" s="12" t="inlineStr"/>
       <c r="N67" s="13" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="13" t="n">
@@ -5538,32 +5538,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32492</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Dunkerque] - Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>Commune de Dunkerque</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5578,27 +5578,27 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32498</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00162004</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>436.38</v>
+        <v>142.1</v>
       </c>
       <c r="O68" s="17" t="n">
         <v>0</v>
@@ -5610,12 +5610,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32492</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Dunkerque] - Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
@@ -5657,57 +5657,57 @@
         <v>3</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32498</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162004</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>5000</v>
+        <v>436.38</v>
       </c>
       <c r="O69" s="17" t="n">
-        <v>2802</v>
+        <v>0</v>
       </c>
       <c r="P69" s="13" t="n">
-        <v>386.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5717,49 +5717,49 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="O70" s="16" t="n">
-        <v>882.5</v>
+        <v>5000</v>
+      </c>
+      <c r="O70" s="17" t="n">
+        <v>2802</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0</v>
+        <v>386.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32438</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)] - Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -5801,15 +5801,23 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L71" s="12" t="inlineStr"/>
-      <c r="M71" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32446</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>00161842</t>
+        </is>
+      </c>
       <c r="N71" s="13" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>0</v>
+        <v>882.5</v>
       </c>
       <c r="P71" s="13" t="n">
         <v>0</v>
@@ -5818,27 +5826,27 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32426</t>
+          <t>PDMDEP-32438</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Extraction en masse des restitutions</t>
+          <t>[DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)] - Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Extraction en masse des restitutions</t>
+          <t>Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5848,7 +5856,7 @@
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
@@ -5858,25 +5866,17 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32430</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
-          <t>00161695</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr"/>
+      <c r="M72" s="15" t="inlineStr"/>
       <c r="N72" s="16" t="n">
         <v>0</v>
       </c>
@@ -5890,12 +5890,12 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32426</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[DIJON METROPOLE] - Extraction en masse des restitutions</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Extraction en masse des restitutions</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -5937,57 +5937,57 @@
         <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32430</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161695</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>666.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -5997,69 +5997,69 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>8.5</v>
+        <v>0.75</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>3150</v>
+        <v>0</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>3150</v>
+        <v>500</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>370.59</v>
+        <v>666.67</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6069,69 +6069,69 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>11.25</v>
+        <v>8.5</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>910</v>
+        <v>3150</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>1683.5</v>
+        <v>3150</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>149.64</v>
+        <v>370.59</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6141,64 +6141,64 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>2</v>
+        <v>11.25</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O76" s="16" t="n">
-        <v>255</v>
+        <v>1683.5</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>127.5</v>
+        <v>149.64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6225,52 +6225,52 @@
         <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>500</v>
+        <v>255</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>1950</v>
+        <v>255</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>780</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
@@ -6301,33 +6301,33 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O78" s="17" t="n">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="O78" s="16" t="n">
+        <v>1950</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6357,69 +6357,69 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>350.5</v>
+        <v>590.15</v>
       </c>
       <c r="O79" s="17" t="n">
-        <v>43.35</v>
+        <v>0</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>86.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6429,64 +6429,64 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>3.75</v>
+        <v>0.5</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>440.38</v>
+        <v>350.5</v>
       </c>
       <c r="O80" s="17" t="n">
-        <v>0</v>
+        <v>43.35</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32009</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>[TULLE AGGLO] Accomp modélisation</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
@@ -6513,14 +6513,22 @@
         <v>3</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L81" s="12" t="inlineStr"/>
-      <c r="M81" s="12" t="inlineStr"/>
+        <v>3.75</v>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32046</t>
+        </is>
+      </c>
+      <c r="M81" s="12" t="inlineStr">
+        <is>
+          <t>00160148</t>
+        </is>
+      </c>
       <c r="N81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="13" t="n">
+        <v>440.38</v>
+      </c>
+      <c r="O81" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="13" t="n">
@@ -6530,37 +6538,37 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32009</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>[TULLE AGGLO] Accomp modélisation</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
@@ -6570,64 +6578,56 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32002</t>
-        </is>
-      </c>
-      <c r="M82" s="15" t="inlineStr">
-        <is>
-          <t>00160078</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr"/>
       <c r="N82" s="16" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="O82" s="16" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6642,44 +6642,44 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="P83" s="13" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6714,30 +6714,30 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>600</v>
-      </c>
-      <c r="O84" s="17" t="n">
-        <v>480</v>
+        <v>0</v>
+      </c>
+      <c r="O84" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
         <v>0</v>
@@ -6746,32 +6746,32 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6797,19 +6797,19 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>360</v>
+        <v>600</v>
       </c>
       <c r="O85" s="17" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="P85" s="13" t="n">
         <v>0</v>
@@ -6818,27 +6818,27 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
@@ -6865,20 +6865,20 @@
         <v>3</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>588</v>
+        <v>360</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6890,27 +6890,27 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6925,35 +6925,35 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O87" s="13" t="n">
-        <v>203.5</v>
+        <v>588</v>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
         <v>0</v>
@@ -6962,12 +6962,12 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -6997,35 +6997,35 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O88" s="17" t="n">
-        <v>0</v>
+        <v>203.5</v>
+      </c>
+      <c r="O88" s="16" t="n">
+        <v>203.5</v>
       </c>
       <c r="P88" s="16" t="n">
         <v>0</v>
@@ -7034,32 +7034,32 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31555</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[TALMONT SAINT HILAIRE] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE TALMONT SAINT HILAIRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Nouveau client Littéralis Expert</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7069,64 +7069,64 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31562</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00157906</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="13" t="n">
-        <v>-437</v>
+        <v>450</v>
+      </c>
+      <c r="O89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>-79.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31555</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[TALMONT SAINT HILAIRE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE TALMONT SAINT HILAIRE</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Nouveau client Littéralis Expert</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7141,69 +7141,69 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31562</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157906</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>2400</v>
-      </c>
-      <c r="O90" s="17" t="n">
-        <v>1826.65</v>
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>-437</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>135.31</v>
+        <v>-79.45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -7213,69 +7213,69 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0.25</v>
+        <v>13.5</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>0</v>
+        <v>2400</v>
+      </c>
+      <c r="O91" s="17" t="n">
+        <v>1826.65</v>
       </c>
       <c r="P91" s="13" t="n">
-        <v>0</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7285,34 +7285,34 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>6.25</v>
+        <v>0.25</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>472.005</v>
-      </c>
-      <c r="O92" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7322,32 +7322,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7357,35 +7357,35 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>210</v>
-      </c>
-      <c r="O93" s="13" t="n">
-        <v>210</v>
+        <v>472.005</v>
+      </c>
+      <c r="O93" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
         <v>0</v>
@@ -7394,27 +7394,27 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -7441,23 +7441,23 @@
         <v>4</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="P94" s="16" t="n">
         <v>0</v>
@@ -7466,27 +7466,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
@@ -7513,57 +7513,57 @@
         <v>4</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>843</v>
-      </c>
-      <c r="O95" s="17" t="n">
-        <v>562</v>
+        <v>0</v>
+      </c>
+      <c r="O95" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>449.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7573,64 +7573,64 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O96" s="16" t="n">
-        <v>71.2</v>
+        <v>843</v>
+      </c>
+      <c r="O96" s="17" t="n">
+        <v>562</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0</v>
+        <v>449.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7650,30 +7650,30 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
+        <v>71.2</v>
       </c>
       <c r="O97" s="13" t="n">
-        <v>0</v>
+        <v>71.2</v>
       </c>
       <c r="P97" s="13" t="n">
         <v>0</v>
@@ -7682,32 +7682,32 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
@@ -7717,35 +7717,35 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
         <v>0</v>
@@ -7754,12 +7754,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
@@ -7805,19 +7805,19 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O99" s="13" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="P99" s="13" t="n">
         <v>0</v>
@@ -7826,12 +7826,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7866,30 +7866,30 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O100" s="17" t="n">
-        <v>0</v>
+        <v>255</v>
+      </c>
+      <c r="O100" s="16" t="n">
+        <v>255</v>
       </c>
       <c r="P100" s="16" t="n">
         <v>0</v>
@@ -7898,12 +7898,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -7938,30 +7938,30 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="O101" s="13" t="n">
-        <v>140</v>
+        <v>500</v>
+      </c>
+      <c r="O101" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
         <v>0</v>
@@ -7970,27 +7970,27 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -8010,64 +8010,64 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>266.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8077,49 +8077,49 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O103" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>0</v>
+        <v>266.67</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
@@ -8154,30 +8154,30 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>700</v>
-      </c>
-      <c r="O104" s="17" t="n">
-        <v>350</v>
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
         <v>0</v>
@@ -8186,27 +8186,27 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -8233,23 +8233,23 @@
         <v>5</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="O105" s="17" t="n">
+        <v>350</v>
       </c>
       <c r="P105" s="13" t="n">
         <v>0</v>
@@ -8258,27 +8258,27 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H106" s="15" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8330,27 +8330,27 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -8377,16 +8377,16 @@
         <v>5</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8402,12 +8402,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
@@ -8442,29 +8442,29 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>4.42</v>
+        <v>1.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>67.215</v>
-      </c>
-      <c r="O108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8525,16 +8525,16 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>250</v>
+        <v>67.215</v>
       </c>
       <c r="O109" s="17" t="n">
         <v>0</v>
@@ -8597,18 +8597,18 @@
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O110" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8618,32 +8618,32 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29480</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES - Migration V2</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -8653,35 +8653,35 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29485</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00145493</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>-133</v>
+        <v>0</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>-434</v>
+        <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
         <v>0</v>
@@ -8690,27 +8690,27 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29480</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t>COMMUNE D'EYSINES - Migration V2</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
+          <t>COMMUNE D'EYSINES</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
@@ -8725,35 +8725,35 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29485</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00145493</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
+        <v>-133</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>0</v>
+        <v>-434</v>
       </c>
       <c r="P112" s="16" t="n">
         <v>0</v>
@@ -8762,30 +8762,32 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29191</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[CD 01]  - Audit Technique BDD On Prem</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>Commune de Calais</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8795,7 +8797,7 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
@@ -8807,23 +8809,23 @@
         <v>6</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29193</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00148281</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
         <v>0</v>
@@ -8832,22 +8834,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29191</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>[CD 01]  - Audit Technique BDD On Prem</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8870,30 +8872,30 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29193</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00148281</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O114" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="P114" s="16" t="n">
         <v>0</v>
@@ -8902,12 +8904,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -8917,7 +8919,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8940,64 +8942,62 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>5.25</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="13" t="n">
-        <v>127.8</v>
+        <v>157.5</v>
+      </c>
+      <c r="O115" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>24.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v/>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
@@ -9007,38 +9007,38 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O116" s="16" t="n">
-        <v>0</v>
+        <v>127.8</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="117">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
@@ -9107,39 +9107,41 @@
         <v>0</v>
       </c>
       <c r="O117" s="13" t="n">
-        <v>1360</v>
+        <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>453.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
@@ -9149,49 +9151,49 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>9.25</v>
+        <v>3</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="O118" s="16" t="n">
-        <v>1651.54</v>
+        <v>1360</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>178.54</v>
+        <v>453.33</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9201,13 +9203,11 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v/>
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
@@ -9226,33 +9226,33 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>4.7</v>
+        <v>9.25</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>690</v>
-      </c>
-      <c r="O119" s="17" t="n">
-        <v>415</v>
+        <v>1250</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>1651.54</v>
       </c>
       <c r="P119" s="13" t="n">
-        <v>88.3</v>
+        <v>178.54</v>
       </c>
     </row>
     <row r="120">
@@ -9309,22 +9309,22 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>1762.5</v>
+        <v>690</v>
       </c>
       <c r="O120" s="17" t="n">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>79.79000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="121">
@@ -9381,22 +9381,22 @@
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>895</v>
+        <v>1762.5</v>
       </c>
       <c r="O121" s="17" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="P121" s="13" t="n">
-        <v>0</v>
+        <v>79.79000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -9453,18 +9453,18 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>895</v>
+      </c>
+      <c r="O122" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9546,12 +9546,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9561,11 +9561,13 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
@@ -9579,28 +9581,28 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9616,12 +9618,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9631,7 +9633,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9649,34 +9651,34 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="O125" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9686,12 +9688,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9701,38 +9703,52 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F126" s="15" t="inlineStr"/>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F126" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr"/>
-      <c r="M126" s="15" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27557</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>00144532</t>
+        </is>
+      </c>
       <c r="N126" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>800</v>
+      </c>
+      <c r="O126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9742,12 +9758,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26825</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9757,27 +9773,21 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v/>
-      </c>
-      <c r="F127" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr"/>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr"/>
       <c r="I127" s="12" t="inlineStr">
         <is>
           <t>05/11/2025</t>
@@ -9789,16 +9799,8 @@
       <c r="K127" s="12" t="n">
         <v>1.75</v>
       </c>
-      <c r="L127" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-26826</t>
-        </is>
-      </c>
-      <c r="M127" s="12" t="inlineStr">
-        <is>
-          <t>00142974</t>
-        </is>
-      </c>
+      <c r="L127" s="12" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr"/>
       <c r="N127" s="13" t="n">
         <v>0</v>
       </c>
@@ -9812,28 +9814,26 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26825</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>VILLE DE COLOMBES</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v/>
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
@@ -9847,63 +9847,65 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>34.25</v>
+        <v>1.75</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26826</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00142974</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O128" s="16" t="n">
-        <v>353.88</v>
+        <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>10.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
@@ -9922,60 +9924,58 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>9.75</v>
+        <v>34.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O129" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O129" s="13" t="n">
+        <v>353.88</v>
       </c>
       <c r="P129" s="13" t="n">
-        <v>0</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v/>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
@@ -9994,29 +9994,29 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.75</v>
+        <v>9.75</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -10026,12 +10026,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24410</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)] - Modélisation et paramétrage</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10041,11 +10041,13 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
@@ -10059,65 +10061,63 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27379</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>499344</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O131" s="13" t="n">
-        <v>596.7</v>
+        <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
-        <v>477.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24410</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)] - Modélisation et paramétrage</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E132" s="15" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNAUTE D'AGGLOMERATION DE CERGY PONTOISE (CACP)</t>
+        </is>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v/>
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr">
@@ -10136,50 +10136,60 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr"/>
-      <c r="M132" s="15" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27379</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>499344</t>
+        </is>
+      </c>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O132" s="16" t="n">
-        <v>0</v>
+        <v>596.7</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>0</v>
+        <v>477.36</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
@@ -10188,35 +10198,27 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr"/>
       <c r="N133" s="13" t="n">
         <v>0</v>
       </c>
@@ -10279,12 +10281,12 @@
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10300,22 +10302,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23940</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE TOULOUSE - GEODP2 migration</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE TOULOUSE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10323,7 +10325,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -10333,35 +10335,35 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28056</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>496529</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O135" s="13" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="P135" s="13" t="n">
         <v>0</v>
@@ -10370,22 +10372,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23940</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>MAIRIE DE TOULOUSE - GEODP2 migration</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>MAIRIE DE TOULOUSE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10393,7 +10395,7 @@
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G136" s="15" t="inlineStr">
@@ -10403,59 +10405,59 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28056</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>496529</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
-        <v>6000</v>
-      </c>
-      <c r="O136" s="17" t="n">
-        <v>2080.938</v>
+        <v>0</v>
+      </c>
+      <c r="O136" s="16" t="n">
+        <v>825</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>160.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23521</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- 4 EXPORTS FILIENS</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10463,7 +10465,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -10473,59 +10475,59 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>28/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28054</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>495929</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="13" t="n">
-        <v>0</v>
+        <v>6000</v>
+      </c>
+      <c r="O137" s="17" t="n">
+        <v>2080.938</v>
       </c>
       <c r="P137" s="13" t="n">
-        <v>0</v>
+        <v>160.07</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23410</t>
+          <t>PDMDEP-23521</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+          <t>METROPOLE TOULON- 4 EXPORTS FILIENS</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10533,32 +10535,40 @@
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>28/07/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr"/>
-      <c r="M138" s="15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28054</t>
+        </is>
+      </c>
+      <c r="M138" s="15" t="inlineStr">
+        <is>
+          <t>495929</t>
+        </is>
+      </c>
       <c r="N138" s="16" t="n">
         <v>0</v>
       </c>
@@ -10572,22 +10582,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23410</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10600,35 +10610,27 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27570</t>
-        </is>
-      </c>
-      <c r="M139" s="12" t="inlineStr">
-        <is>
-          <t>493613</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr"/>
+      <c r="M139" s="12" t="inlineStr"/>
       <c r="N139" s="13" t="n">
         <v>0</v>
       </c>
@@ -10642,22 +10644,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10675,28 +10677,28 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
@@ -10712,22 +10714,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10745,12 +10747,12 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
@@ -10761,12 +10763,12 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
@@ -10831,12 +10833,12 @@
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
@@ -10867,7 +10869,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10901,22 +10903,22 @@
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O143" s="13" t="n">
-        <v>131.25</v>
+        <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -10937,7 +10939,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10971,43 +10973,43 @@
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
-        <v>3121.2</v>
+        <v>0</v>
       </c>
       <c r="O144" s="16" t="n">
-        <v>3121.2</v>
+        <v>131.25</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>2080.8</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11015,7 +11017,7 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -11025,59 +11027,59 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
-        <v>1000</v>
+        <v>3121.2</v>
       </c>
       <c r="O145" s="13" t="n">
-        <v>1930.88</v>
+        <v>3121.2</v>
       </c>
       <c r="P145" s="13" t="n">
-        <v>0</v>
+        <v>2080.8</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11085,7 +11087,7 @@
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G146" s="15" t="inlineStr">
@@ -11095,35 +11097,35 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O146" s="16" t="n">
-        <v>0</v>
+        <v>1930.88</v>
       </c>
       <c r="P146" s="16" t="n">
         <v>0</v>
@@ -11132,22 +11134,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11165,59 +11167,59 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O147" s="17" t="n">
-        <v>250</v>
+        <v>0</v>
+      </c>
+      <c r="O147" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P147" s="13" t="n">
-        <v>83.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11240,54 +11242,54 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
-        <v>161</v>
-      </c>
-      <c r="O148" s="16" t="n">
-        <v>391</v>
+        <v>500</v>
+      </c>
+      <c r="O148" s="17" t="n">
+        <v>250</v>
       </c>
       <c r="P148" s="16" t="n">
-        <v>260.67</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20528</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] Nettoyage env Littéralis Expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>COLOMBES</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11303,39 +11305,51 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H149" s="12" t="inlineStr"/>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L149" s="12" t="inlineStr"/>
-      <c r="M149" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L149" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N149" s="13" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="O149" s="13" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="P149" s="13" t="n">
-        <v>0</v>
+        <v>260.67</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20528</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[COLOMBES] Nettoyage env Littéralis Expert</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
@@ -11345,7 +11359,7 @@
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>COLOMBES</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11364,14 +11378,14 @@
       <c r="H150" s="15" t="inlineStr"/>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11388,22 +11402,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11419,32 +11433,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H151" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H151" s="12" t="inlineStr"/>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
@@ -11458,12 +11460,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11473,7 +11475,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11491,28 +11493,28 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
@@ -11528,12 +11530,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11543,7 +11545,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11561,34 +11563,34 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>6.5</v>
+        <v>2.25</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>702.33</v>
-      </c>
-      <c r="O153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11598,12 +11600,12 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -11613,7 +11615,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11636,29 +11638,29 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="16" t="n">
+        <v>702.33</v>
+      </c>
+      <c r="O154" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P154" s="16" t="n">
@@ -11668,22 +11670,22 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18687</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[Andernos les Bains] Paramétrage "vrai" module Terrasses / remplacement Placier déguisé</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>ANDERNOS-LES-BAINS</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11691,7 +11693,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -11701,28 +11703,28 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0.75</v>
+        <v>4.75</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28022</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>451939</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N155" s="13" t="n">
@@ -11738,12 +11740,12 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18242</t>
+          <t>PDMDEP-18687</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[Mont Saint Aignan] Placier Presta : acquisition</t>
+          <t>[Andernos les Bains] Paramétrage "vrai" module Terrasses / remplacement Placier déguisé</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
@@ -11753,7 +11755,7 @@
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>MONT SAINT AIGNAN</t>
+          <t>ANDERNOS-LES-BAINS</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11771,28 +11773,28 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K156" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28021</t>
+          <t>PDMDEP-28022</t>
         </is>
       </c>
       <c r="M156" s="15" t="inlineStr">
         <is>
-          <t>404496</t>
+          <t>451939</t>
         </is>
       </c>
       <c r="N156" s="16" t="n">
@@ -11808,22 +11810,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18242</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Mont Saint Aignan] Placier Presta : acquisition</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>MONT SAINT AIGNAN</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11831,12 +11833,12 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -11853,10 +11855,18 @@
         <v>18</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L157" s="12" t="inlineStr"/>
-      <c r="M157" s="12" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L157" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28021</t>
+        </is>
+      </c>
+      <c r="M157" s="12" t="inlineStr">
+        <is>
+          <t>404496</t>
+        </is>
+      </c>
       <c r="N157" s="13" t="n">
         <v>0</v>
       </c>
@@ -11870,22 +11880,22 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11893,7 +11903,7 @@
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G158" s="15" t="inlineStr">
@@ -11915,7 +11925,7 @@
         <v>18</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>11.75</v>
+        <v>5</v>
       </c>
       <c r="L158" s="15" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -11932,12 +11942,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -11947,7 +11957,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -11960,40 +11970,32 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M159" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>11.75</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr"/>
+      <c r="M159" s="12" t="inlineStr"/>
       <c r="N159" s="13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="O159" s="13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P159" s="13" t="n">
         <v>0</v>
@@ -12002,22 +12004,22 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12025,7 +12027,7 @@
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G160" s="15" t="inlineStr">
@@ -12035,35 +12037,35 @@
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
         <v>18</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N160" s="16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="O160" s="16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="P160" s="16" t="n">
         <v>0</v>
@@ -12072,12 +12074,12 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
@@ -12087,7 +12089,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E161" s="12" t="n">
@@ -12117,16 +12119,16 @@
         <v>18</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N161" s="13" t="n">
@@ -12142,12 +12144,12 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-17594</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CD 40 LANDES] Param Interfaces + dev spé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
@@ -12157,7 +12159,7 @@
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CD 40</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12180,30 +12182,30 @@
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L162" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28016</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M162" s="15" t="inlineStr">
         <is>
-          <t>453168</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N162" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O162" s="16" t="n">
-        <v>239.25</v>
+        <v>0</v>
       </c>
       <c r="P162" s="16" t="n">
         <v>0</v>
@@ -12212,12 +12214,12 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-17291</t>
+          <t>PDMDEP-17594</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[EVREUX] Littéralis Expert</t>
+          <t>[CD 40 LANDES] Param Interfaces + dev spé</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
@@ -12227,7 +12229,7 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>EVREUX</t>
+          <t>CD 40</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12245,35 +12247,35 @@
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>29/10/2024</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="J163" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K163" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L163" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27496</t>
+          <t>PDMDEP-28016</t>
         </is>
       </c>
       <c r="M163" s="12" t="inlineStr">
         <is>
-          <t>450556</t>
+          <t>453168</t>
         </is>
       </c>
       <c r="N163" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O163" s="13" t="n">
-        <v>1650</v>
+        <v>239.25</v>
       </c>
       <c r="P163" s="13" t="n">
         <v>0</v>
@@ -12282,22 +12284,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-17291</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[EVREUX] Littéralis Expert</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>EVREUX</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12305,37 +12307,45 @@
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L164" s="15" t="inlineStr"/>
-      <c r="M164" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27496</t>
+        </is>
+      </c>
+      <c r="M164" s="15" t="inlineStr">
+        <is>
+          <t>450556</t>
+        </is>
+      </c>
       <c r="N164" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O164" s="16" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="P164" s="16" t="n">
         <v>0</v>
@@ -12344,22 +12354,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16116</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>CD 01</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12367,7 +12377,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -12377,19 +12387,19 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L165" s="12" t="inlineStr"/>
       <c r="M165" s="12" t="inlineStr"/>
@@ -12406,22 +12416,22 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16116</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AME</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CD 01</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12444,14 +12454,14 @@
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L166" s="15" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -12468,22 +12478,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12506,14 +12516,14 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>15.25</v>
+        <v>0.5</v>
       </c>
       <c r="L167" s="12" t="inlineStr"/>
       <c r="M167" s="12" t="inlineStr"/>
@@ -12530,22 +12540,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12563,19 +12573,19 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>0.5</v>
+        <v>15.25</v>
       </c>
       <c r="L168" s="15" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -12592,22 +12602,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12625,19 +12635,19 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12654,12 +12664,12 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
@@ -12669,7 +12679,7 @@
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12687,19 +12697,19 @@
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
         <v>31</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L170" s="15" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -12716,22 +12726,22 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E171" s="12" t="n">
@@ -12754,14 +12764,14 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L171" s="12" t="inlineStr"/>
       <c r="M171" s="12" t="inlineStr"/>
@@ -12778,22 +12788,22 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E172" s="15" t="n">
@@ -12806,35 +12816,27 @@
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="L172" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M172" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L172" s="15" t="inlineStr"/>
+      <c r="M172" s="15" t="inlineStr"/>
       <c r="N172" s="16" t="n">
         <v>0</v>
       </c>
@@ -12848,22 +12850,22 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E173" s="12" t="n">
@@ -12879,20 +12881,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H173" s="12" t="inlineStr"/>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L173" s="12" t="inlineStr"/>
-      <c r="M173" s="12" t="inlineStr"/>
+        <v>11.25</v>
+      </c>
+      <c r="L173" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M173" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N173" s="13" t="n">
         <v>0</v>
       </c>
@@ -12906,12 +12920,12 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr">
@@ -12921,7 +12935,7 @@
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E174" s="15" t="n">
@@ -12934,24 +12948,20 @@
       </c>
       <c r="G174" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H174" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H174" s="15" t="inlineStr"/>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -12968,12 +12978,12 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -12983,7 +12993,7 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E175" s="12" t="n">
@@ -13006,14 +13016,14 @@
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13030,28 +13040,26 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E176" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E176" s="15" t="n">
+        <v/>
       </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
@@ -13077,7 +13085,7 @@
         <v>33</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>1.25</v>
+        <v>18.5</v>
       </c>
       <c r="L176" s="15" t="inlineStr"/>
       <c r="M176" s="15" t="inlineStr"/>
@@ -13094,12 +13102,12 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
@@ -13109,12 +13117,12 @@
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -13129,7 +13137,7 @@
       </c>
       <c r="H177" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I177" s="12" t="inlineStr">
@@ -13141,7 +13149,7 @@
         <v>33</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="L177" s="12" t="inlineStr"/>
       <c r="M177" s="12" t="inlineStr"/>
@@ -13158,23 +13166,27 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C178" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C178" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E178" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F178" s="15" t="inlineStr">
@@ -13189,19 +13201,19 @@
       </c>
       <c r="H178" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="L178" s="15" t="inlineStr"/>
       <c r="M178" s="15" t="inlineStr"/>
@@ -13218,36 +13230,50 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-4703</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>[Amelie Les Bains Palalda - Placier v2 + Paiement CB] GEODP V2</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr"/>
-      <c r="D179" s="12" t="inlineStr"/>
-      <c r="E179" s="12" t="n">
-        <v/>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E179" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G179" s="12" t="inlineStr"/>
-      <c r="H179" s="12" t="inlineStr"/>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>02/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>1</v>
+        <v>5.75</v>
       </c>
       <c r="L179" s="12" t="inlineStr"/>
       <c r="M179" s="12" t="inlineStr"/>
@@ -13264,52 +13290,36 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-4137</t>
+          <t>PDMDEP-4703</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>[NIORT] LITTERALIS PRIME</t>
-        </is>
-      </c>
-      <c r="C180" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D180" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE NIORT</t>
-        </is>
-      </c>
+          <t>[Amelie Les Bains Palalda - Placier v2 + Paiement CB] GEODP V2</t>
+        </is>
+      </c>
+      <c r="C180" s="15" t="inlineStr"/>
+      <c r="D180" s="15" t="inlineStr"/>
       <c r="E180" s="15" t="n">
         <v/>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G180" s="15" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H180" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G180" s="15" t="inlineStr"/>
+      <c r="H180" s="15" t="inlineStr"/>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>27/08/2023</t>
+          <t>02/09/2023</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L180" s="15" t="inlineStr"/>
       <c r="M180" s="15" t="inlineStr"/>
@@ -13326,12 +13336,12 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-4137</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[NIORT] LITTERALIS PRIME</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
@@ -13341,13 +13351,11 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E181" s="12" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
+          <t>COMMUNE DE NIORT</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v/>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
@@ -13361,12 +13369,12 @@
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>27/08/2023</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
@@ -13390,21 +13398,29 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
-        </is>
-      </c>
-      <c r="C182" s="15" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
-        </is>
-      </c>
-      <c r="E182" s="15" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F182" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13412,20 +13428,24 @@
       </c>
       <c r="G182" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H182" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H182" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13442,18 +13462,18 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr"/>
@@ -13470,7 +13490,7 @@
       <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
@@ -13494,18 +13514,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1294</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13522,7 +13542,7 @@
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
@@ -13546,18 +13566,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1294</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13598,18 +13618,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13626,14 +13646,14 @@
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L186" s="15" t="inlineStr"/>
       <c r="M186" s="15" t="inlineStr"/>
@@ -13650,18 +13670,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1278</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13678,7 +13698,7 @@
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
@@ -13702,18 +13722,18 @@
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1278</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13724,7 +13744,7 @@
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr"/>
@@ -13739,20 +13759,12 @@
       <c r="K188" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L188" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M188" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+      <c r="L188" s="15" t="inlineStr"/>
+      <c r="M188" s="15" t="inlineStr"/>
       <c r="N188" s="16" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="O188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P188" s="16" t="n">
@@ -13762,18 +13774,18 @@
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13784,48 +13796,56 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L189" s="12" t="inlineStr"/>
-      <c r="M189" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L189" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N189" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O189" s="13" t="n">
-        <v>0</v>
+        <v>1191.4</v>
+      </c>
+      <c r="O189" s="17" t="n">
+        <v>170.2</v>
       </c>
       <c r="P189" s="13" t="n">
-        <v>0</v>
+        <v>340.4</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1257</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13842,14 +13862,14 @@
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L190" s="15" t="inlineStr"/>
       <c r="M190" s="15" t="inlineStr"/>
@@ -13866,18 +13886,18 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1252</t>
+          <t>PSC-1257</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -13894,14 +13914,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -13918,18 +13938,18 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>PSC-1245</t>
+          <t>PSC-1252</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="E192" s="15" t="inlineStr"/>
@@ -13970,18 +13990,18 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1245</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr"/>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr"/>
@@ -13992,56 +14012,48 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr"/>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="J193" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K193" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L193" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33167</t>
-        </is>
-      </c>
-      <c r="M193" s="12" t="inlineStr">
-        <is>
-          <t>00165437</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L193" s="12" t="inlineStr"/>
+      <c r="M193" s="12" t="inlineStr"/>
       <c r="N193" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O193" s="17" t="n">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="O193" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P193" s="13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C194" s="15" t="inlineStr"/>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E194" s="15" t="inlineStr"/>
@@ -14058,30 +14070,30 @@
       <c r="H194" s="15" t="inlineStr"/>
       <c r="I194" s="15" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J194" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K194" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L194" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M194" s="15" t="inlineStr">
         <is>
-          <t>00163534</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N194" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="O194" s="16" t="n">
-        <v>50</v>
+        <v>500</v>
+      </c>
+      <c r="O194" s="17" t="n">
+        <v>400</v>
       </c>
       <c r="P194" s="16" t="n">
         <v>200</v>
@@ -14090,18 +14102,18 @@
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>PSC-1197</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr"/>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr"/>
@@ -14112,48 +14124,56 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr"/>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J195" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K195" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L195" s="12" t="inlineStr"/>
-      <c r="M195" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L195" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M195" s="12" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N195" s="13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O195" s="13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P195" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1197</t>
         </is>
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="C196" s="15" t="inlineStr"/>
       <c r="D196" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E196" s="15" t="inlineStr"/>
@@ -14170,14 +14190,14 @@
       <c r="H196" s="15" t="inlineStr"/>
       <c r="I196" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J196" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K196" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L196" s="15" t="inlineStr"/>
       <c r="M196" s="15" t="inlineStr"/>
@@ -14194,18 +14214,18 @@
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr"/>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr"/>
@@ -14222,14 +14242,14 @@
       <c r="H197" s="12" t="inlineStr"/>
       <c r="I197" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J197" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K197" s="12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L197" s="12" t="inlineStr"/>
       <c r="M197" s="12" t="inlineStr"/>
@@ -14246,16 +14266,20 @@
     <row r="198">
       <c r="A198" s="14" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1147</t>
         </is>
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>Commune de COUTANCES</t>
         </is>
       </c>
       <c r="C198" s="15" t="inlineStr"/>
-      <c r="D198" s="15" t="inlineStr"/>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
       <c r="E198" s="15" t="inlineStr"/>
       <c r="F198" s="15" t="inlineStr">
         <is>
@@ -14264,7 +14288,7 @@
       </c>
       <c r="G198" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H198" s="15" t="inlineStr"/>
@@ -14277,23 +14301,15 @@
         <v>4</v>
       </c>
       <c r="K198" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31452</t>
-        </is>
-      </c>
-      <c r="M198" s="15" t="inlineStr">
-        <is>
-          <t>00156409</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L198" s="15" t="inlineStr"/>
+      <c r="M198" s="15" t="inlineStr"/>
       <c r="N198" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O198" s="16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P198" s="16" t="n">
         <v>0</v>
@@ -14302,20 +14318,16 @@
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1145</t>
         </is>
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE BOLBEC</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr"/>
-      <c r="D199" s="12" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
+      <c r="D199" s="12" t="inlineStr"/>
       <c r="E199" s="12" t="inlineStr"/>
       <c r="F199" s="12" t="inlineStr">
         <is>
@@ -14324,28 +14336,36 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr"/>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J199" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K199" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L199" s="12" t="inlineStr"/>
-      <c r="M199" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L199" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31452</t>
+        </is>
+      </c>
+      <c r="M199" s="12" t="inlineStr">
+        <is>
+          <t>00156409</t>
+        </is>
+      </c>
       <c r="N199" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O199" s="13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P199" s="13" t="n">
         <v>0</v>
@@ -14354,18 +14374,18 @@
     <row r="200">
       <c r="A200" s="14" t="inlineStr">
         <is>
-          <t>PSC-817</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>PLATEAU D'HAUTEVILLE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C200" s="15" t="inlineStr"/>
       <c r="D200" s="15" t="inlineStr">
         <is>
-          <t>PLATEAU D'HAUTEVILLE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E200" s="15" t="inlineStr"/>
@@ -14382,14 +14402,14 @@
       <c r="H200" s="15" t="inlineStr"/>
       <c r="I200" s="15" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J200" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K200" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L200" s="15" t="inlineStr"/>
       <c r="M200" s="15" t="inlineStr"/>
@@ -14406,18 +14426,18 @@
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-817</t>
         </is>
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>PLATEAU D'HAUTEVILLE</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr"/>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>PLATEAU D'HAUTEVILLE</t>
         </is>
       </c>
       <c r="E201" s="12" t="inlineStr"/>
@@ -14434,14 +14454,14 @@
       <c r="H201" s="12" t="inlineStr"/>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="J201" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K201" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L201" s="12" t="inlineStr"/>
       <c r="M201" s="12" t="inlineStr"/>
@@ -14456,31 +14476,83 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="18" t="inlineStr">
+      <c r="A202" s="14" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B202" s="15" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C202" s="15" t="inlineStr"/>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E202" s="15" t="inlineStr"/>
+      <c r="F202" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G202" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H202" s="15" t="inlineStr"/>
+      <c r="I202" s="15" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J202" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K202" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L202" s="15" t="inlineStr"/>
+      <c r="M202" s="15" t="inlineStr"/>
+      <c r="N202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B202" s="18" t="inlineStr"/>
-      <c r="C202" s="18" t="inlineStr"/>
-      <c r="D202" s="18" t="inlineStr"/>
-      <c r="E202" s="18" t="inlineStr"/>
-      <c r="F202" s="18" t="inlineStr"/>
-      <c r="G202" s="18" t="inlineStr"/>
-      <c r="H202" s="18" t="inlineStr"/>
-      <c r="I202" s="18" t="inlineStr"/>
-      <c r="J202" s="18" t="inlineStr"/>
-      <c r="K202" s="18" t="inlineStr"/>
-      <c r="L202" s="18" t="inlineStr"/>
-      <c r="M202" s="18" t="inlineStr"/>
-      <c r="N202" s="19" t="n">
+      <c r="B203" s="18" t="inlineStr"/>
+      <c r="C203" s="18" t="inlineStr"/>
+      <c r="D203" s="18" t="inlineStr"/>
+      <c r="E203" s="18" t="inlineStr"/>
+      <c r="F203" s="18" t="inlineStr"/>
+      <c r="G203" s="18" t="inlineStr"/>
+      <c r="H203" s="18" t="inlineStr"/>
+      <c r="I203" s="18" t="inlineStr"/>
+      <c r="J203" s="18" t="inlineStr"/>
+      <c r="K203" s="18" t="inlineStr"/>
+      <c r="L203" s="18" t="inlineStr"/>
+      <c r="M203" s="18" t="inlineStr"/>
+      <c r="N203" s="19" t="n">
         <v>66535.84</v>
       </c>
-      <c r="O202" s="19" t="n">
-        <v>69339.33799999999</v>
-      </c>
-      <c r="P202" s="19" t="n">
-        <v>140.15</v>
+      <c r="O203" s="19" t="n">
+        <v>71354.13800000001</v>
+      </c>
+      <c r="P203" s="19" t="n">
+        <v>144.22</v>
       </c>
     </row>
   </sheetData>
@@ -14683,6 +14755,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16010,16 +16083,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>393665</v>
+        <v>391650</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>199704</v>
+        <v>186951</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>193961</v>
+        <v>204699</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>162601</v>
+        <v>173339</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16035,10 +16108,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>194570</v>
+        <v>192755</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>90065</v>
+        <v>88250</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16060,16 +16133,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>199095</v>
+        <v>198895</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>109639</v>
+        <v>98701</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>89456</v>
+        <v>100194</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>65605</v>
+        <v>76343</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>

--- a/jira_export_2026-06-30.xlsx
+++ b/jira_export_2026-06-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>71,354 €</t>
+          <t>73,090 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>26,179 €</t>
+          <t>26,691 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>45,175 €</t>
+          <t>46,399 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>778 h</t>
+          <t>793 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -898,7 +898,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P203"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>895</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>325.45</v>
+        <v>298.33</v>
       </c>
     </row>
     <row r="39">
@@ -4534,9 +4534,9 @@
         </is>
       </c>
       <c r="N53" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O53" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="O53" s="13" t="n">
         <v>720</v>
       </c>
       <c r="P53" s="13" t="n">
@@ -4606,9 +4606,9 @@
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="O54" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="O54" s="16" t="n">
         <v>320</v>
       </c>
       <c r="P54" s="16" t="n">
@@ -4898,32 +4898,32 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32902</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t xml:space="preserve">COMMANDE PAX </t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
@@ -4949,19 +4949,19 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32910</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00159637</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="O59" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="P59" s="13" t="n">
         <v>0</v>
@@ -4970,27 +4970,27 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32902</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BALARUC-LES-BAINS ] - COMMANDE PAX </t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE BALARUCL-LES-BAINS </t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMANDE PAX </t>
+          <t>MIGRATION SIMPLE GEODP PLACIER</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5005,64 +5005,64 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32910</t>
+          <t>PDMDEP-32869</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00159637</t>
+          <t>00164607</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>50</v>
+        <v>490</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>343</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32860</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLACIER</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LE LUC EN PROVENCE</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>MIGRATION SIMPLE GEODP PLACIER</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -5077,49 +5077,49 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32869</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00164607</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>490</v>
+        <v>300</v>
       </c>
       <c r="O61" s="17" t="n">
-        <v>343</v>
+        <v>150</v>
       </c>
       <c r="P61" s="13" t="n">
-        <v>68.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5154,59 +5154,59 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O62" s="17" t="n">
-        <v>150</v>
+        <v>800</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>2560</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0</v>
+        <v>787.6900000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5221,69 +5221,69 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>800</v>
+        <v>1984.5</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>2560</v>
+        <v>1984.5</v>
       </c>
       <c r="P63" s="13" t="n">
-        <v>1024</v>
+        <v>360.82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5293,69 +5293,69 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>5.5</v>
+        <v>1.25</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>1984.5</v>
-      </c>
-      <c r="O64" s="16" t="n">
-        <v>1984.5</v>
+        <v>1371</v>
+      </c>
+      <c r="O64" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>360.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
@@ -5377,109 +5377,101 @@
         <v>2</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>1371</v>
+        <v>3864</v>
       </c>
       <c r="O65" s="17" t="n">
-        <v>0</v>
+        <v>2484</v>
       </c>
       <c r="P65" s="13" t="n">
-        <v>0</v>
+        <v>709.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32607</t>
-        </is>
-      </c>
-      <c r="M66" s="15" t="inlineStr">
-        <is>
-          <t>00163155</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L66" s="15" t="inlineStr"/>
+      <c r="M66" s="15" t="inlineStr"/>
       <c r="N66" s="16" t="n">
-        <v>3864</v>
-      </c>
-      <c r="O66" s="17" t="n">
-        <v>2484</v>
+        <v>0</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>709.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5489,12 +5481,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5504,7 +5496,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -5521,14 +5513,22 @@
         <v>2</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L67" s="12" t="inlineStr"/>
-      <c r="M67" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="inlineStr">
+        <is>
+          <t>00162313</t>
+        </is>
+      </c>
       <c r="N67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="13" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O67" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="13" t="n">
@@ -5538,32 +5538,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32492</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[Commune de Dunkerque] - Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>Commune de Dunkerque</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5578,27 +5578,27 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32498</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00162004</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>142.1</v>
+        <v>436.38</v>
       </c>
       <c r="O68" s="17" t="n">
         <v>0</v>
@@ -5610,12 +5610,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32492</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Dunkerque] - Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Commune de Dunkerque</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Mise en service paiement CB sur régie/module GEODP "Domanialité Publique"</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
@@ -5657,57 +5657,57 @@
         <v>3</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32498</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00162004</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>436.38</v>
+        <v>5000</v>
       </c>
       <c r="O69" s="17" t="n">
-        <v>0</v>
+        <v>2802</v>
       </c>
       <c r="P69" s="13" t="n">
-        <v>0</v>
+        <v>386.48</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5717,49 +5717,49 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>5000</v>
-      </c>
-      <c r="O70" s="17" t="n">
-        <v>2802</v>
+        <v>882.5</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>882.5</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>386.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32438</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)] - Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -5801,23 +5801,15 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32446</t>
-        </is>
-      </c>
-      <c r="M71" s="12" t="inlineStr">
-        <is>
-          <t>00161842</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L71" s="12" t="inlineStr"/>
+      <c r="M71" s="12" t="inlineStr"/>
       <c r="N71" s="13" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>882.5</v>
+        <v>0</v>
       </c>
       <c r="P71" s="13" t="n">
         <v>0</v>
@@ -5826,27 +5818,27 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32438</t>
+          <t>PDMDEP-32426</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)] - Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
+          <t>[DIJON METROPOLE] - Extraction en masse des restitutions</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES PYRENEES ORIENTALES (CD 66)</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Licence SHERPA SD - et Installation Sherpa PDEF existante clé numérique</t>
+          <t>Extraction en masse des restitutions</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5856,7 +5848,7 @@
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
@@ -5866,17 +5858,25 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L72" s="15" t="inlineStr"/>
-      <c r="M72" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32430</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>00161695</t>
+        </is>
+      </c>
       <c r="N72" s="16" t="n">
         <v>0</v>
       </c>
@@ -5890,12 +5890,12 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32426</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Extraction en masse des restitutions</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Extraction en masse des restitutions</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -5937,57 +5937,57 @@
         <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32430</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161695</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>0</v>
+        <v>666.67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -5997,69 +5997,69 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.75</v>
+        <v>8.5</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>0</v>
+        <v>3150</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>500</v>
+        <v>3150</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>666.67</v>
+        <v>370.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6069,69 +6069,69 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>8.5</v>
+        <v>11.25</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>3150</v>
+        <v>1683.5</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>3150</v>
+        <v>1683.5</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>370.59</v>
+        <v>149.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6141,64 +6141,64 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>11.25</v>
+        <v>2</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="O76" s="16" t="n">
-        <v>1683.5</v>
+        <v>255</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>149.64</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6225,52 +6225,52 @@
         <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>255</v>
+        <v>500</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>255</v>
+        <v>1950</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>127.5</v>
+        <v>780</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
@@ -6301,33 +6301,33 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O78" s="16" t="n">
-        <v>1950</v>
+        <v>590.15</v>
+      </c>
+      <c r="O78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6357,69 +6357,69 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>590.15</v>
+        <v>350.5</v>
       </c>
       <c r="O79" s="17" t="n">
-        <v>0</v>
+        <v>43.35</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>0</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6429,64 +6429,64 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0.5</v>
+        <v>3.75</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="O80" s="17" t="n">
-        <v>43.35</v>
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>86.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32009</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>[TULLE AGGLO] Accomp modélisation</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
@@ -6513,22 +6513,14 @@
         <v>3</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L81" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32046</t>
-        </is>
-      </c>
-      <c r="M81" s="12" t="inlineStr">
-        <is>
-          <t>00160148</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L81" s="12" t="inlineStr"/>
+      <c r="M81" s="12" t="inlineStr"/>
       <c r="N81" s="13" t="n">
-        <v>440.38</v>
-      </c>
-      <c r="O81" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="13" t="n">
@@ -6538,37 +6530,37 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32009</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>[TULLE AGGLO] Accomp modélisation</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
@@ -6578,56 +6570,64 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L82" s="15" t="inlineStr"/>
-      <c r="M82" s="15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32002</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>00160078</t>
+        </is>
+      </c>
       <c r="N82" s="16" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6642,44 +6642,44 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="P83" s="13" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6714,30 +6714,30 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="O84" s="16" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="P84" s="16" t="n">
         <v>0</v>
@@ -6746,32 +6746,32 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6797,19 +6797,19 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="O85" s="17" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="P85" s="13" t="n">
         <v>0</v>
@@ -6818,27 +6818,27 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
@@ -6865,20 +6865,20 @@
         <v>3</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>360</v>
+        <v>588</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6890,27 +6890,27 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6925,35 +6925,35 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>588</v>
-      </c>
-      <c r="O87" s="17" t="n">
-        <v>0</v>
+        <v>203.5</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>203.5</v>
       </c>
       <c r="P87" s="13" t="n">
         <v>0</v>
@@ -6962,12 +6962,12 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -6997,35 +6997,35 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O88" s="16" t="n">
-        <v>203.5</v>
+        <v>450</v>
+      </c>
+      <c r="O88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P88" s="16" t="n">
         <v>0</v>
@@ -7034,32 +7034,32 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31555</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[TALMONT SAINT HILAIRE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE TALMONT SAINT HILAIRE</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Nouveau client Littéralis Expert</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7069,64 +7069,64 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31562</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00157906</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>450</v>
-      </c>
-      <c r="O89" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>-437</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>0</v>
+        <v>-79.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31555</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[TALMONT SAINT HILAIRE] - Déploiement Littéralis Expert</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE TALMONT SAINT HILAIRE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Nouveau client Littéralis Expert</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7141,69 +7141,69 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31562</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157906</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>0</v>
+        <v>1826.65</v>
       </c>
       <c r="O90" s="16" t="n">
-        <v>-437</v>
+        <v>1826.65</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>-79.45</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -7213,69 +7213,69 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>13.5</v>
+        <v>0.25</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>2400</v>
-      </c>
-      <c r="O91" s="17" t="n">
-        <v>1826.65</v>
+        <v>0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P91" s="13" t="n">
-        <v>135.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7285,34 +7285,34 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0.25</v>
+        <v>6.25</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>472.005</v>
+      </c>
+      <c r="O92" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7322,32 +7322,32 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7357,35 +7357,35 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>472.005</v>
-      </c>
-      <c r="O93" s="17" t="n">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="O93" s="13" t="n">
+        <v>210</v>
       </c>
       <c r="P93" s="13" t="n">
         <v>0</v>
@@ -7394,27 +7394,27 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -7441,23 +7441,23 @@
         <v>4</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
         <v>0</v>
@@ -7466,27 +7466,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
@@ -7513,57 +7513,57 @@
         <v>4</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
-        <v>0</v>
+        <v>843</v>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>562</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>0</v>
+        <v>449.6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7573,64 +7573,64 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>843</v>
-      </c>
-      <c r="O96" s="17" t="n">
-        <v>562</v>
+        <v>71.2</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>71.2</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>449.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7650,30 +7650,30 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>71.2</v>
+        <v>0</v>
       </c>
       <c r="O97" s="13" t="n">
-        <v>71.2</v>
+        <v>0</v>
       </c>
       <c r="P97" s="13" t="n">
         <v>0</v>
@@ -7682,32 +7682,32 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
@@ -7717,35 +7717,35 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="P98" s="16" t="n">
         <v>0</v>
@@ -7754,12 +7754,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
@@ -7805,19 +7805,19 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O99" s="13" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="P99" s="13" t="n">
         <v>0</v>
@@ -7826,12 +7826,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7866,30 +7866,30 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="O100" s="16" t="n">
-        <v>255</v>
+        <v>500</v>
+      </c>
+      <c r="O100" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
         <v>0</v>
@@ -7898,12 +7898,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -7938,30 +7938,30 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O101" s="17" t="n">
-        <v>0</v>
+        <v>140</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>140</v>
       </c>
       <c r="P101" s="13" t="n">
         <v>0</v>
@@ -7970,27 +7970,27 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -8010,64 +8010,64 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>0</v>
+        <v>266.67</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8077,49 +8077,49 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O103" s="13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>266.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
@@ -8154,30 +8154,30 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="O104" s="16" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="P104" s="16" t="n">
         <v>0</v>
@@ -8186,27 +8186,27 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -8233,23 +8233,23 @@
         <v>5</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="O105" s="17" t="n">
-        <v>350</v>
+        <v>0</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
         <v>0</v>
@@ -8258,27 +8258,27 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H106" s="15" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8330,27 +8330,27 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -8377,16 +8377,16 @@
         <v>5</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8402,12 +8402,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
@@ -8442,29 +8442,29 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>1.25</v>
+        <v>4.42</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>67.215</v>
+      </c>
+      <c r="O108" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8525,16 +8525,16 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>67.215</v>
+        <v>250</v>
       </c>
       <c r="O109" s="17" t="n">
         <v>0</v>
@@ -8597,18 +8597,18 @@
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8618,32 +8618,32 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29480</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE D'EYSINES - Migration V2</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE D'EYSINES</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -8653,35 +8653,35 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29485</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145493</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>0</v>
+        <v>-133</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>0</v>
+        <v>-434</v>
       </c>
       <c r="P111" s="13" t="n">
         <v>0</v>
@@ -8690,27 +8690,27 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29480</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES - Migration V2</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'EYSINES</t>
+          <t>Commune de Calais</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
@@ -8725,35 +8725,35 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29485</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00145493</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>-133</v>
+        <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>-434</v>
+        <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
         <v>0</v>
@@ -8762,32 +8762,30 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29191</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t>[CD 01]  - Audit Technique BDD On Prem</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v/>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8797,7 +8795,7 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
@@ -8809,23 +8807,23 @@
         <v>6</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29193</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00148281</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P113" s="13" t="n">
         <v>0</v>
@@ -8834,22 +8832,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29191</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[CD 01]  - Audit Technique BDD On Prem</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8872,30 +8870,30 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29193</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00148281</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
         <v>0</v>
@@ -8904,12 +8902,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -8919,7 +8917,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8942,62 +8940,64 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.25</v>
+        <v>5.25</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O115" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>127.8</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>0</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
@@ -9007,38 +9007,38 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O116" s="16" t="n">
-        <v>127.8</v>
+        <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>24.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
@@ -9107,36 +9107,36 @@
         <v>0</v>
       </c>
       <c r="O117" s="13" t="n">
-        <v>0</v>
+        <v>1360</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>0</v>
+        <v>453.33</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28237</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>VILLE DE VANNES - SEPA pour activité marché</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E118" s="15" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>SEPA pour activité marché</t>
         </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
@@ -9151,38 +9151,38 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28238</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145118</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O118" s="16" t="n">
-        <v>1360</v>
+        <v>0</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>453.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="N119" s="13" t="n">
-        <v>1250</v>
+        <v>1651.54</v>
       </c>
       <c r="O119" s="13" t="n">
         <v>1651.54</v>
@@ -9318,9 +9318,9 @@
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>690</v>
-      </c>
-      <c r="O120" s="17" t="n">
+        <v>415</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>415</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9390,9 +9390,9 @@
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>1762.5</v>
-      </c>
-      <c r="O121" s="17" t="n">
+        <v>375</v>
+      </c>
+      <c r="O121" s="13" t="n">
         <v>375</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9462,9 +9462,9 @@
         </is>
       </c>
       <c r="N122" s="16" t="n">
-        <v>895</v>
-      </c>
-      <c r="O122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9746,13 +9746,13 @@
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="O126" s="17" t="n">
-        <v>0</v>
+        <v>512</v>
+      </c>
+      <c r="O126" s="16" t="n">
+        <v>512</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="127">
@@ -10014,9 +10014,9 @@
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -10500,7 +10500,7 @@
         </is>
       </c>
       <c r="N137" s="13" t="n">
-        <v>6000</v>
+        <v>2080.94</v>
       </c>
       <c r="O137" s="17" t="n">
         <v>2080.938</v>
@@ -11262,9 +11262,9 @@
         </is>
       </c>
       <c r="N148" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O148" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="O148" s="16" t="n">
         <v>250</v>
       </c>
       <c r="P148" s="16" t="n">
@@ -11855,7 +11855,7 @@
         <v>18</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
@@ -11871,10 +11871,10 @@
         <v>0</v>
       </c>
       <c r="O157" s="13" t="n">
-        <v>0</v>
+        <v>1054</v>
       </c>
       <c r="P157" s="13" t="n">
-        <v>0</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="158">
@@ -11987,7 +11987,7 @@
         <v>18</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>11.75</v>
+        <v>13.75</v>
       </c>
       <c r="L159" s="12" t="inlineStr"/>
       <c r="M159" s="12" t="inlineStr"/>
@@ -13290,16 +13290,24 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-4703</t>
+          <t>PDMDEP-6023</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>[Amelie Les Bains Palalda - Placier v2 + Paiement CB] GEODP V2</t>
-        </is>
-      </c>
-      <c r="C180" s="15" t="inlineStr"/>
-      <c r="D180" s="15" t="inlineStr"/>
+          <t>[SOTTEVILLE LES ROUEN - SEPA] GEODP V2</t>
+        </is>
+      </c>
+      <c r="C180" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D180" s="15" t="inlineStr">
+        <is>
+          <t>SOTTEVILLE LES ROUENS</t>
+        </is>
+      </c>
       <c r="E180" s="15" t="n">
         <v/>
       </c>
@@ -13308,11 +13316,19 @@
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G180" s="15" t="inlineStr"/>
-      <c r="H180" s="15" t="inlineStr"/>
+      <c r="G180" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H180" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>02/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
@@ -13336,52 +13352,36 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-4137</t>
+          <t>PDMDEP-4703</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>[NIORT] LITTERALIS PRIME</t>
-        </is>
-      </c>
-      <c r="C181" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D181" s="12" t="inlineStr">
-        <is>
-          <t>COMMUNE DE NIORT</t>
-        </is>
-      </c>
+          <t>[Amelie Les Bains Palalda - Placier v2 + Paiement CB] GEODP V2</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr"/>
+      <c r="D181" s="12" t="inlineStr"/>
       <c r="E181" s="12" t="n">
         <v/>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G181" s="12" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H181" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G181" s="12" t="inlineStr"/>
+      <c r="H181" s="12" t="inlineStr"/>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>27/08/2023</t>
+          <t>02/09/2023</t>
         </is>
       </c>
       <c r="J181" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13398,12 +13398,12 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-4137</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[NIORT] LITTERALIS PRIME</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr">
@@ -13413,13 +13413,11 @@
       </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E182" s="15" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
+          <t>COMMUNE DE NIORT</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v/>
       </c>
       <c r="F182" s="15" t="inlineStr">
         <is>
@@ -13433,12 +13431,12 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>27/08/2023</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
@@ -13462,21 +13460,29 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-1305</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
-        </is>
-      </c>
-      <c r="C183" s="12" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MORHANGE</t>
-        </is>
-      </c>
-      <c r="E183" s="12" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13484,20 +13490,24 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H183" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L183" s="12" t="inlineStr"/>
       <c r="M183" s="12" t="inlineStr"/>
@@ -13514,18 +13524,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1300</t>
+          <t>PSC-1305</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE JONZAC</t>
+          <t>MAIRIE DE MORHANGE</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13542,7 +13552,7 @@
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
@@ -13566,18 +13576,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1294</t>
+          <t>PSC-1300</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NANTEUIL LES MEAUX</t>
+          <t>COMMUNE DE JONZAC</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13594,7 +13604,7 @@
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
@@ -13618,18 +13628,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1294</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>VILLE DE NANTEUIL LES MEAUX</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13670,18 +13680,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13698,14 +13708,14 @@
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L187" s="12" t="inlineStr"/>
       <c r="M187" s="12" t="inlineStr"/>
@@ -13722,18 +13732,18 @@
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1278</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>Mairie Le Tholonet</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13750,7 +13760,7 @@
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
@@ -13774,18 +13784,18 @@
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1278</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie Le Tholonet</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13796,7 +13806,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
@@ -13811,41 +13821,33 @@
       <c r="K189" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L189" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M189" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+      <c r="L189" s="12" t="inlineStr"/>
+      <c r="M189" s="12" t="inlineStr"/>
       <c r="N189" s="13" t="n">
-        <v>1191.4</v>
-      </c>
-      <c r="O189" s="17" t="n">
-        <v>170.2</v>
+        <v>0</v>
+      </c>
+      <c r="O189" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P189" s="13" t="n">
-        <v>340.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1264</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE COURNONSEC</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13856,48 +13858,56 @@
       </c>
       <c r="G190" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L190" s="15" t="inlineStr"/>
-      <c r="M190" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L190" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M190" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N190" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O190" s="16" t="n">
-        <v>0</v>
+        <v>1191.4</v>
+      </c>
+      <c r="O190" s="17" t="n">
+        <v>170.2</v>
       </c>
       <c r="P190" s="16" t="n">
-        <v>0</v>
+        <v>340.4</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1257</t>
+          <t>PSC-1264</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA VILLE DU BOIS</t>
+          <t>COMMUNE DE COURNONSEC</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -13914,14 +13924,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -13938,18 +13948,18 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>PSC-1252</t>
+          <t>PSC-1257</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ETUPES</t>
+          <t>MAIRIE DE LA VILLE DU BOIS</t>
         </is>
       </c>
       <c r="E192" s="15" t="inlineStr"/>
@@ -13966,14 +13976,14 @@
       <c r="H192" s="15" t="inlineStr"/>
       <c r="I192" s="15" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="J192" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K192" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L192" s="15" t="inlineStr"/>
       <c r="M192" s="15" t="inlineStr"/>
@@ -13990,18 +14000,18 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>PSC-1245</t>
+          <t>PSC-1252</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr"/>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>COMMUNE D'ETUPES</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr"/>
@@ -14042,18 +14052,18 @@
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1245</t>
         </is>
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="C194" s="15" t="inlineStr"/>
       <c r="D194" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E194" s="15" t="inlineStr"/>
@@ -14064,56 +14074,48 @@
       </c>
       <c r="G194" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H194" s="15" t="inlineStr"/>
       <c r="I194" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="J194" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K194" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L194" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33167</t>
-        </is>
-      </c>
-      <c r="M194" s="15" t="inlineStr">
-        <is>
-          <t>00165437</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L194" s="15" t="inlineStr"/>
+      <c r="M194" s="15" t="inlineStr"/>
       <c r="N194" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O194" s="17" t="n">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="O194" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P194" s="16" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr"/>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr"/>
@@ -14130,30 +14132,30 @@
       <c r="H195" s="12" t="inlineStr"/>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J195" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K195" s="12" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L195" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32829</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M195" s="12" t="inlineStr">
         <is>
-          <t>00163534</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N195" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O195" s="13" t="n">
-        <v>50</v>
+        <v>500</v>
+      </c>
+      <c r="O195" s="17" t="n">
+        <v>400</v>
       </c>
       <c r="P195" s="13" t="n">
         <v>200</v>
@@ -14162,18 +14164,18 @@
     <row r="196">
       <c r="A196" s="14" t="inlineStr">
         <is>
-          <t>PSC-1197</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C196" s="15" t="inlineStr"/>
       <c r="D196" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E196" s="15" t="inlineStr"/>
@@ -14184,48 +14186,56 @@
       </c>
       <c r="G196" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H196" s="15" t="inlineStr"/>
       <c r="I196" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J196" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K196" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L196" s="15" t="inlineStr"/>
-      <c r="M196" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L196" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32829</t>
+        </is>
+      </c>
+      <c r="M196" s="15" t="inlineStr">
+        <is>
+          <t>00163534</t>
+        </is>
+      </c>
       <c r="N196" s="16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O196" s="16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P196" s="16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1197</t>
         </is>
       </c>
       <c r="B197" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr"/>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr"/>
@@ -14242,14 +14252,14 @@
       <c r="H197" s="12" t="inlineStr"/>
       <c r="I197" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J197" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K197" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197" s="12" t="inlineStr"/>
       <c r="M197" s="12" t="inlineStr"/>
@@ -14266,18 +14276,18 @@
     <row r="198">
       <c r="A198" s="14" t="inlineStr">
         <is>
-          <t>PSC-1147</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C198" s="15" t="inlineStr"/>
       <c r="D198" s="15" t="inlineStr">
         <is>
-          <t>Commune de COUTANCES</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E198" s="15" t="inlineStr"/>
@@ -14294,14 +14304,14 @@
       <c r="H198" s="15" t="inlineStr"/>
       <c r="I198" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J198" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K198" s="15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L198" s="15" t="inlineStr"/>
       <c r="M198" s="15" t="inlineStr"/>
@@ -14318,16 +14328,20 @@
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t>PSC-1145</t>
+          <t>PSC-1147</t>
         </is>
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOLBEC</t>
+          <t>Commune de COUTANCES</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr"/>
-      <c r="D199" s="12" t="inlineStr"/>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>Commune de COUTANCES</t>
+        </is>
+      </c>
       <c r="E199" s="12" t="inlineStr"/>
       <c r="F199" s="12" t="inlineStr">
         <is>
@@ -14336,7 +14350,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr"/>
@@ -14349,23 +14363,15 @@
         <v>4</v>
       </c>
       <c r="K199" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-31452</t>
-        </is>
-      </c>
-      <c r="M199" s="12" t="inlineStr">
-        <is>
-          <t>00156409</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L199" s="12" t="inlineStr"/>
+      <c r="M199" s="12" t="inlineStr"/>
       <c r="N199" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O199" s="13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P199" s="13" t="n">
         <v>0</v>
@@ -14374,20 +14380,16 @@
     <row r="200">
       <c r="A200" s="14" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1145</t>
         </is>
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE BOLBEC</t>
         </is>
       </c>
       <c r="C200" s="15" t="inlineStr"/>
-      <c r="D200" s="15" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
+      <c r="D200" s="15" t="inlineStr"/>
       <c r="E200" s="15" t="inlineStr"/>
       <c r="F200" s="15" t="inlineStr">
         <is>
@@ -14396,28 +14398,36 @@
       </c>
       <c r="G200" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H200" s="15" t="inlineStr"/>
       <c r="I200" s="15" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J200" s="15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K200" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L200" s="15" t="inlineStr"/>
-      <c r="M200" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L200" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31452</t>
+        </is>
+      </c>
+      <c r="M200" s="15" t="inlineStr">
+        <is>
+          <t>00156409</t>
+        </is>
+      </c>
       <c r="N200" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O200" s="16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P200" s="16" t="n">
         <v>0</v>
@@ -14426,18 +14436,18 @@
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
         <is>
-          <t>PSC-817</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>PLATEAU D'HAUTEVILLE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr"/>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>PLATEAU D'HAUTEVILLE</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E201" s="12" t="inlineStr"/>
@@ -14454,14 +14464,14 @@
       <c r="H201" s="12" t="inlineStr"/>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J201" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K201" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L201" s="12" t="inlineStr"/>
       <c r="M201" s="12" t="inlineStr"/>
@@ -14478,18 +14488,18 @@
     <row r="202">
       <c r="A202" s="14" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-817</t>
         </is>
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>PLATEAU D'HAUTEVILLE</t>
         </is>
       </c>
       <c r="C202" s="15" t="inlineStr"/>
       <c r="D202" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>PLATEAU D'HAUTEVILLE</t>
         </is>
       </c>
       <c r="E202" s="15" t="inlineStr"/>
@@ -14506,14 +14516,14 @@
       <c r="H202" s="15" t="inlineStr"/>
       <c r="I202" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="J202" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K202" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L202" s="15" t="inlineStr"/>
       <c r="M202" s="15" t="inlineStr"/>
@@ -14528,31 +14538,83 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="18" t="inlineStr">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr"/>
+      <c r="D203" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E203" s="12" t="inlineStr"/>
+      <c r="F203" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G203" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H203" s="12" t="inlineStr"/>
+      <c r="I203" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J203" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K203" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L203" s="12" t="inlineStr"/>
+      <c r="M203" s="12" t="inlineStr"/>
+      <c r="N203" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B203" s="18" t="inlineStr"/>
-      <c r="C203" s="18" t="inlineStr"/>
-      <c r="D203" s="18" t="inlineStr"/>
-      <c r="E203" s="18" t="inlineStr"/>
-      <c r="F203" s="18" t="inlineStr"/>
-      <c r="G203" s="18" t="inlineStr"/>
-      <c r="H203" s="18" t="inlineStr"/>
-      <c r="I203" s="18" t="inlineStr"/>
-      <c r="J203" s="18" t="inlineStr"/>
-      <c r="K203" s="18" t="inlineStr"/>
-      <c r="L203" s="18" t="inlineStr"/>
-      <c r="M203" s="18" t="inlineStr"/>
-      <c r="N203" s="19" t="n">
-        <v>66535.84</v>
-      </c>
-      <c r="O203" s="19" t="n">
-        <v>71354.13800000001</v>
-      </c>
-      <c r="P203" s="19" t="n">
-        <v>144.22</v>
+      <c r="B204" s="18" t="inlineStr"/>
+      <c r="C204" s="18" t="inlineStr"/>
+      <c r="D204" s="18" t="inlineStr"/>
+      <c r="E204" s="18" t="inlineStr"/>
+      <c r="F204" s="18" t="inlineStr"/>
+      <c r="G204" s="18" t="inlineStr"/>
+      <c r="H204" s="18" t="inlineStr"/>
+      <c r="I204" s="18" t="inlineStr"/>
+      <c r="J204" s="18" t="inlineStr"/>
+      <c r="K204" s="18" t="inlineStr"/>
+      <c r="L204" s="18" t="inlineStr"/>
+      <c r="M204" s="18" t="inlineStr"/>
+      <c r="N204" s="19" t="n">
+        <v>57265.59</v>
+      </c>
+      <c r="O204" s="19" t="n">
+        <v>73090.13800000001</v>
+      </c>
+      <c r="P204" s="19" t="n">
+        <v>145.31</v>
       </c>
     </row>
   </sheetData>
@@ -14756,6 +14818,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId199"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15937,7 +16000,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>272.25</v>
+        <v>272.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>59.75</v>
@@ -15946,7 +16009,7 @@
         <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>347.5</v>
+        <v>347.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>107.75</v>
@@ -15956,7 +16019,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -15967,26 +16030,26 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>129.5</v>
+        <v>134.5</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>144.5</v>
+        <v>152.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>19.5</v>
+        <v>20.25</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>271.99</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -15998,7 +16061,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>152</v>
+        <v>157.5</v>
       </c>
     </row>
   </sheetData>
@@ -16083,16 +16146,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>391650</v>
+        <v>389914</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>186951</v>
+        <v>186269</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>204699</v>
+        <v>203645</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>173339</v>
+        <v>172285</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>15760</v>
@@ -16108,10 +16171,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>192755</v>
+        <v>192243</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>88250</v>
+        <v>87738</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16133,16 +16196,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>198895</v>
+        <v>197671</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>98701</v>
+        <v>98531</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>100194</v>
+        <v>99140</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>76343</v>
+        <v>75289</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
@@ -17879,7 +17942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -17900,7 +17963,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26 clôture(s) : 20 projet(s), 6 rework</t>
+          <t>27 clôture(s) : 21 projet(s), 6 rework</t>
         </is>
       </c>
     </row>
@@ -18538,49 +18601,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-17131</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>[PAU] Migration GEODP</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>PAU</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="n">
-        <v>20</v>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33566</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-21265</t>
+          <t>PDMDEP-17131</t>
         </is>
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
+          <t>[PAU] Migration GEODP</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>SANARY SUR MER</t>
+          <t>PAU</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -18594,23 +18657,23 @@
         </is>
       </c>
       <c r="F26" s="28" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-23419</t>
+          <t>PDMDEP-21265</t>
         </is>
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN - GEODP2 migratio</t>
+          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN</t>
+          <t>SANARY SUR MER</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -18624,28 +18687,28 @@
         </is>
       </c>
       <c r="F27" s="28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-14779</t>
+          <t>PDMDEP-23419</t>
         </is>
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>[ANTIBES] Réinstallation Littéralis base Test et Prod</t>
+          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN - GEODP2 migratio</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>COMMUNAUTE D’AGGLOMERATION DU GRAND VERDUN</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -18654,23 +18717,23 @@
         </is>
       </c>
       <c r="F28" s="28" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-23410</t>
+          <t>PDMDEP-14779</t>
         </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+          <t>[ANTIBES] Réinstallation Littéralis base Test et Prod</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -18684,65 +18747,95 @@
         </is>
       </c>
       <c r="F29" s="28" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-23410</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-24216</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F31" s="28" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="29" t="n"/>
-      <c r="E33" s="29" t="n"/>
-      <c r="F33" s="29" t="n">
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n">
         <v>6</v>
       </c>
     </row>

--- a/jira_export_2026-06-30.xlsx
+++ b/jira_export_2026-06-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>73,090 €</t>
+          <t>73,765 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>26,691 €</t>
+          <t>26,941 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>46,399 €</t>
+          <t>46,824 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>793 h</t>
+          <t>797 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -3617,10 +3617,10 @@
         <v>708</v>
       </c>
       <c r="O40" s="16" t="n">
-        <v>1416</v>
+        <v>1840.8</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>809.14</v>
+        <v>1051.89</v>
       </c>
     </row>
     <row r="41">
@@ -8017,7 +8017,7 @@
         <v>5</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>200</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>266.67</v>
+        <v>114.29</v>
       </c>
     </row>
     <row r="103">
@@ -9733,7 +9733,7 @@
         <v>7</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>512</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>73.14</v>
+        <v>56.89</v>
       </c>
     </row>
     <row r="127">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr"/>
@@ -13769,16 +13769,24 @@
       <c r="K188" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L188" s="15" t="inlineStr"/>
-      <c r="M188" s="15" t="inlineStr"/>
+      <c r="L188" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M188" s="15" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N188" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O188" s="16" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189">
@@ -14611,10 +14619,10 @@
         <v>57265.59</v>
       </c>
       <c r="O204" s="19" t="n">
-        <v>73090.13800000001</v>
+        <v>73764.93799999999</v>
       </c>
       <c r="P204" s="19" t="n">
-        <v>145.31</v>
+        <v>145.78</v>
       </c>
     </row>
   </sheetData>
@@ -16000,16 +16008,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>272.5</v>
+        <v>275</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>59.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>347.75</v>
+        <v>349.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>107.75</v>
@@ -16019,7 +16027,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16038,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>134.5</v>
+        <v>135.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>17</v>
@@ -16039,7 +16047,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>152.5</v>
+        <v>153.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>20.25</v>
@@ -16049,7 +16057,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16069,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>157.5</v>
+        <v>158.25</v>
       </c>
     </row>
   </sheetData>
@@ -16146,10 +16154,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>389914</v>
+        <v>389739</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>186269</v>
+        <v>186095</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>203645</v>
@@ -16171,10 +16179,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>192243</v>
+        <v>192493</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>87738</v>
+        <v>87988</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104505</v>
@@ -16196,10 +16204,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>197671</v>
+        <v>197246</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>98531</v>
+        <v>98106</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>99140</v>
@@ -16225,7 +16233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16249,7 +16257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 35 commande(s)</t>
+          <t>Épics créées ce mois — 36 commande(s)</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16312,12 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -16319,7 +16327,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -16339,7 +16347,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -16664,22 +16672,22 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33980</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33976</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PRIEST</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -16689,7 +16697,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -16699,22 +16707,22 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00170407</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-33980</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-33976</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -16724,7 +16732,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE SAINT PRIEST</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -16734,7 +16742,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -16744,32 +16752,32 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170407</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>1700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -16789,32 +16797,32 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>3370</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -16834,32 +16842,32 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>3500</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -16879,32 +16887,32 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -16914,7 +16922,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -16924,32 +16932,32 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -16962,35 +16970,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr"/>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>32077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -17010,7 +17022,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
@@ -17020,22 +17032,22 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -17045,42 +17057,38 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr"/>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>0</v>
+        <v>32077</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -17100,32 +17108,32 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>4250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -17135,7 +17143,7 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -17145,32 +17153,32 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>1414.5</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -17180,7 +17188,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -17190,32 +17198,32 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -17235,32 +17243,32 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>1775</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -17270,7 +17278,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -17280,37 +17288,37 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>500</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -17318,25 +17326,29 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr"/>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>2625</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -17346,7 +17358,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -17359,29 +17371,25 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G28" s="12" t="inlineStr"/>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>1095.5</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -17391,7 +17399,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -17411,32 +17419,32 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>1890</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -17456,32 +17464,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>6655</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -17501,32 +17509,32 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>895</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -17546,22 +17554,22 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="I32" s="27" t="n">
-        <v>2300</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -17571,7 +17579,7 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -17591,22 +17599,22 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>755</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -17616,7 +17624,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -17636,32 +17644,32 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="I34" s="27" t="n">
-        <v>1000</v>
+        <v>755</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -17681,32 +17689,32 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>1350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -17726,32 +17734,32 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="I36" s="27" t="n">
-        <v>2200</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -17771,32 +17779,32 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>12429</v>
+        <v>895</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -17816,32 +17824,32 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="I38" s="27" t="n">
-        <v>7200</v>
+        <v>12429</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -17861,38 +17869,62 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="I39" s="26" t="n">
-        <v>1840</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>35 commande(s)</t>
-        </is>
-      </c>
-      <c r="I40" s="25" t="n">
-        <v>118111</v>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33944</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33940</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Commune de Thionville</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>00170299</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>2200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -17903,17 +17935,17 @@
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>13 commande(s)</t>
+          <t>36 commande(s)</t>
         </is>
       </c>
       <c r="I41" s="25" t="n">
-        <v>42234</v>
+        <v>118111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B42" s="18" t="n"/>
@@ -17924,10 +17956,31 @@
       <c r="G42" s="18" t="n"/>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>22 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I42" s="25" t="n">
+        <v>42234</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>23 commande(s)</t>
+        </is>
+      </c>
+      <c r="I43" s="25" t="n">
         <v>75876</v>
       </c>
     </row>

--- a/jira_export_2026-06-30.xlsx
+++ b/jira_export_2026-06-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>73,765 €</t>
+          <t>75,568 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>46,824 €</t>
+          <t>48,627 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>797 h</t>
+          <t>805 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1560,11 +1560,11 @@
       <c r="N11" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="O11" s="17" t="n">
-        <v>0</v>
+      <c r="O11" s="13" t="n">
+        <v>720</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12">
@@ -7297,7 +7297,7 @@
         <v>4</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
@@ -8753,10 +8753,10 @@
         <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>0</v>
+        <v>1083.333</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0</v>
+        <v>149.43</v>
       </c>
     </row>
     <row r="113">
@@ -13213,7 +13213,7 @@
         <v>33</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L178" s="15" t="inlineStr"/>
       <c r="M178" s="15" t="inlineStr"/>
@@ -14619,10 +14619,10 @@
         <v>57265.59</v>
       </c>
       <c r="O204" s="19" t="n">
-        <v>73764.93799999999</v>
+        <v>75568.27099999999</v>
       </c>
       <c r="P204" s="19" t="n">
-        <v>145.78</v>
+        <v>148.54</v>
       </c>
     </row>
   </sheetData>
@@ -16008,26 +16008,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>275</v>
+        <v>275.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>59.75</v>
+        <v>61.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>349.75</v>
+        <v>352.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>107.75</v>
+        <v>109.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>581.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
     </row>
@@ -16069,7 +16069,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>158.25</v>
+        <v>161.5</v>
       </c>
     </row>
   </sheetData>
@@ -16154,10 +16154,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>389739</v>
+        <v>387936</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>186095</v>
+        <v>184291</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>203645</v>
@@ -16204,10 +16204,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>197246</v>
+        <v>195443</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>98106</v>
+        <v>96303</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>99140</v>
@@ -16233,7 +16233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16257,7 +16257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 36 commande(s)</t>
+          <t>Épics créées ce mois — 37 commande(s)</t>
         </is>
       </c>
     </row>
@@ -16312,12 +16312,12 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -16852,22 +16852,22 @@
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -16887,32 +16887,32 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>500</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -16932,32 +16932,32 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -16977,32 +16977,32 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>0</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
@@ -17032,22 +17032,22 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -17060,35 +17060,39 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr"/>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>32077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -17108,7 +17112,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
@@ -17118,22 +17122,22 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -17146,39 +17150,35 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G23" s="15" t="inlineStr"/>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>4250</v>
+        <v>32077</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -17198,32 +17198,32 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -17243,32 +17243,32 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>3535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -17288,32 +17288,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1775</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -17333,63 +17333,67 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>1414.5</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr"/>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>2625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -17399,7 +17403,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -17412,29 +17416,25 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G29" s="15" t="inlineStr"/>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>1095.5</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -17464,32 +17464,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>1890</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -17509,32 +17509,32 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>6655</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -17554,11 +17554,11 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I32" s="27" t="n">
-        <v>1840</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="33">
@@ -17789,22 +17789,22 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -17824,32 +17824,32 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="I38" s="27" t="n">
-        <v>12429</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -17869,83 +17869,107 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="I39" s="26" t="n">
-        <v>7200</v>
+        <v>12429</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-34130</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34126</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>00170928</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-33944</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-33940</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Commune de Thionville</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H41" s="15" t="inlineStr">
         <is>
           <t>00170299</t>
         </is>
       </c>
-      <c r="I40" s="27" t="n">
+      <c r="I41" s="26" t="n">
         <v>2200</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="18" t="inlineStr">
-        <is>
-          <t>36 commande(s)</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="n">
-        <v>118111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B42" s="18" t="n"/>
@@ -17956,17 +17980,17 @@
       <c r="G42" s="18" t="n"/>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>13 commande(s)</t>
+          <t>37 commande(s)</t>
         </is>
       </c>
       <c r="I42" s="25" t="n">
-        <v>42234</v>
+        <v>118111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B43" s="18" t="n"/>
@@ -17977,10 +18001,31 @@
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>23 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I43" s="25" t="n">
+        <v>42234</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>24 commande(s)</t>
+        </is>
+      </c>
+      <c r="I44" s="25" t="n">
         <v>75876</v>
       </c>
     </row>
